--- a/CSCI330 Group Project Task Tracker.xlsx
+++ b/CSCI330 Group Project Task Tracker.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30502"/>
-  <workbookPr/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://marietta0-my.sharepoint.com/personal/mca003_marietta_edu/Documents/Junior Year/F26/CSCI330/Group Project/Web-Design-and-Programming-GroupWork/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{2C5AEFBD-5EE4-4783-87B6-0456A0AA740F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="14" documentId="8_{2C5AEFBD-5EE4-4783-87B6-0456A0AA740F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C92F1EB6-8CC2-46E5-8CDC-1ACBC169B15B}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{35008FAE-AE0E-4657-A8AE-48045A98CB38}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="24">
   <si>
     <t>Task</t>
   </si>
@@ -99,13 +99,25 @@
   </si>
   <si>
     <t>Group Peer Evaluations</t>
+  </si>
+  <si>
+    <t>Completed</t>
+  </si>
+  <si>
+    <t>Last Updated</t>
+  </si>
+  <si>
+    <t>Notes</t>
+  </si>
+  <si>
+    <t>HTML done, needs CSS applied</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -142,11 +154,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -481,15 +494,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4840B388-0DE6-4C53-AF10-25A76A976816}">
-  <dimension ref="A1:C12"/>
-  <sheetFormatPr defaultRowHeight="14.45"/>
+  <dimension ref="A1:E12"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="19.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="19.6640625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="21" customWidth="1"/>
-    <col min="3" max="3" width="17.7109375" customWidth="1"/>
+    <col min="3" max="3" width="17.6640625" customWidth="1"/>
+    <col min="4" max="4" width="13.21875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="25.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="15.6">
+    <row r="1" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -499,8 +514,14 @@
       <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="2" spans="1:3">
+      <c r="D1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -508,10 +529,17 @@
         <v>4</v>
       </c>
       <c r="C2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3">
+        <v>20</v>
+      </c>
+      <c r="D2" s="2">
+        <f>DATE(2026,9,17)</f>
+        <v>46282</v>
+      </c>
+      <c r="E2" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>6</v>
       </c>
@@ -522,7 +550,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:3">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>8</v>
       </c>
@@ -533,7 +561,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="1:3">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>9</v>
       </c>
@@ -541,10 +569,17 @@
         <v>4</v>
       </c>
       <c r="C5" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3">
+        <v>20</v>
+      </c>
+      <c r="D5" s="2">
+        <f>DATE(2026,9,17)</f>
+        <v>46282</v>
+      </c>
+      <c r="E5" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>11</v>
       </c>
@@ -555,7 +590,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="7" spans="1:3">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>13</v>
       </c>
@@ -566,7 +601,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="8" spans="1:3">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>14</v>
       </c>
@@ -574,10 +609,14 @@
         <v>4</v>
       </c>
       <c r="C8" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3">
+        <v>5</v>
+      </c>
+      <c r="D8" s="2">
+        <f>DATE(2026,9,17)</f>
+        <v>46282</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>15</v>
       </c>
@@ -588,7 +627,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="10" spans="1:3">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>16</v>
       </c>
@@ -599,7 +638,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="11" spans="1:3">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>17</v>
       </c>
@@ -610,7 +649,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="12" spans="1:3">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>19</v>
       </c>

--- a/CSCI330 Group Project Task Tracker.xlsx
+++ b/CSCI330 Group Project Task Tracker.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30516"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://marietta0-my.sharepoint.com/personal/mca003_marietta_edu/Documents/Junior Year/F26/CSCI330/Group Project/Web-Design-and-Programming-GroupWork/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="14" documentId="8_{2C5AEFBD-5EE4-4783-87B6-0456A0AA740F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C92F1EB6-8CC2-46E5-8CDC-1ACBC169B15B}"/>
+  <xr:revisionPtr revIDLastSave="42" documentId="8_{2C5AEFBD-5EE4-4783-87B6-0456A0AA740F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9DD8A574-737A-40B5-B3E1-BCE002F83E15}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{35008FAE-AE0E-4657-A8AE-48045A98CB38}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="26">
   <si>
     <t>Task</t>
   </si>
@@ -50,48 +50,66 @@
     <t>Progress</t>
   </si>
   <si>
+    <t>Last Updated</t>
+  </si>
+  <si>
+    <t>Notes</t>
+  </si>
+  <si>
     <t>Home page</t>
   </si>
   <si>
     <t>Maisee</t>
   </si>
   <si>
+    <t>Completed</t>
+  </si>
+  <si>
+    <t>HTML done, needs CSS applied</t>
+  </si>
+  <si>
+    <t>Enroll student</t>
+  </si>
+  <si>
+    <t>Beatrice</t>
+  </si>
+  <si>
+    <t>Need to apply CSS</t>
+  </si>
+  <si>
+    <t>Add instructor</t>
+  </si>
+  <si>
+    <t>Add course</t>
+  </si>
+  <si>
+    <t>Register course</t>
+  </si>
+  <si>
+    <t>Drew</t>
+  </si>
+  <si>
+    <t>Drop course</t>
+  </si>
+  <si>
+    <t>CSS</t>
+  </si>
+  <si>
     <t>In progress</t>
   </si>
   <si>
-    <t>Enroll student</t>
-  </si>
-  <si>
-    <t>Beatrice</t>
-  </si>
-  <si>
-    <t>Add instructor</t>
-  </si>
-  <si>
-    <t>Add course</t>
+    <t>Manuals</t>
+  </si>
+  <si>
+    <t>Done with user manual(needs css),started programmer manual</t>
+  </si>
+  <si>
+    <t>README file</t>
   </si>
   <si>
     <t>Not started</t>
   </si>
   <si>
-    <t>Register course</t>
-  </si>
-  <si>
-    <t>Drew</t>
-  </si>
-  <si>
-    <t>Drop course</t>
-  </si>
-  <si>
-    <t>CSS</t>
-  </si>
-  <si>
-    <t>Manuals</t>
-  </si>
-  <si>
-    <t>README file</t>
-  </si>
-  <si>
     <t>AI Usage Report</t>
   </si>
   <si>
@@ -99,25 +117,13 @@
   </si>
   <si>
     <t>Group Peer Evaluations</t>
-  </si>
-  <si>
-    <t>Completed</t>
-  </si>
-  <si>
-    <t>Last Updated</t>
-  </si>
-  <si>
-    <t>Notes</t>
-  </si>
-  <si>
-    <t>HTML done, needs CSS applied</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -495,16 +501,16 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4840B388-0DE6-4C53-AF10-25A76A976816}">
   <dimension ref="A1:E12"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="19.6640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="19.7109375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="21" customWidth="1"/>
-    <col min="3" max="3" width="17.6640625" customWidth="1"/>
-    <col min="4" max="4" width="13.21875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="25.88671875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.7109375" customWidth="1"/>
+    <col min="4" max="4" width="13.28515625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="53.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" ht="15.75">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -515,149 +521,179 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>21</v>
+        <v>3</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
       <c r="A2" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="B2" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C2" t="s">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="D2" s="2">
         <f>DATE(2026,9,17)</f>
         <v>46282</v>
       </c>
       <c r="E2" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
       <c r="A3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D3" s="2">
+        <v>46283</v>
+      </c>
+      <c r="E3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="A4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D4" s="2">
+        <v>46283</v>
+      </c>
+      <c r="E4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
+      <c r="A5" t="s">
+        <v>13</v>
+      </c>
+      <c r="B5" t="s">
         <v>6</v>
       </c>
-      <c r="B3" t="s">
+      <c r="C5" t="s">
         <v>7</v>
-      </c>
-      <c r="C3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>8</v>
-      </c>
-      <c r="B4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C4" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>9</v>
-      </c>
-      <c r="B5" t="s">
-        <v>4</v>
-      </c>
-      <c r="C5" t="s">
-        <v>20</v>
       </c>
       <c r="D5" s="2">
         <f>DATE(2026,9,17)</f>
         <v>46282</v>
       </c>
       <c r="E5" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5">
       <c r="A6" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="B6" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="C6" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+        <v>7</v>
+      </c>
+      <c r="D6" s="2">
+        <v>46284</v>
+      </c>
+      <c r="E6" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5">
       <c r="A7" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="B7" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="C7" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+        <v>7</v>
+      </c>
+      <c r="D7" s="2">
+        <v>46284</v>
+      </c>
+      <c r="E7" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5">
       <c r="A8" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="B8" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C8" t="s">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="D8" s="2">
         <f>DATE(2026,9,17)</f>
         <v>46282</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:5">
       <c r="A9" t="s">
+        <v>19</v>
+      </c>
+      <c r="B9" t="s">
+        <v>10</v>
+      </c>
+      <c r="C9" t="s">
+        <v>18</v>
+      </c>
+      <c r="D9" s="2">
+        <v>46283</v>
+      </c>
+      <c r="E9" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5">
+      <c r="A10" t="s">
+        <v>21</v>
+      </c>
+      <c r="B10" t="s">
         <v>15</v>
       </c>
-      <c r="B9" t="s">
-        <v>7</v>
-      </c>
-      <c r="C9" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
-        <v>16</v>
-      </c>
-      <c r="B10" t="s">
-        <v>12</v>
-      </c>
       <c r="C10" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5">
       <c r="A11" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="B11" t="s">
+        <v>24</v>
+      </c>
+      <c r="C11" t="s">
         <v>18</v>
       </c>
-      <c r="C11" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+    </row>
+    <row r="12" spans="1:5">
       <c r="A12" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="B12" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="C12" t="s">
-        <v>10</v>
+        <v>22</v>
       </c>
     </row>
   </sheetData>

--- a/CSCI330 Group Project Task Tracker.xlsx
+++ b/CSCI330 Group Project Task Tracker.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30516"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30520"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://marietta0-my.sharepoint.com/personal/mca003_marietta_edu/Documents/Junior Year/F26/CSCI330/Group Project/Web-Design-and-Programming-GroupWork/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="42" documentId="8_{2C5AEFBD-5EE4-4783-87B6-0456A0AA740F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9DD8A574-737A-40B5-B3E1-BCE002F83E15}"/>
+  <xr:revisionPtr revIDLastSave="43" documentId="8_{2C5AEFBD-5EE4-4783-87B6-0456A0AA740F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F4F3F39E-77E7-4E3D-9235-29C9185504D7}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{35008FAE-AE0E-4657-A8AE-48045A98CB38}"/>
   </bookViews>
@@ -107,16 +107,16 @@
     <t>README file</t>
   </si>
   <si>
+    <t>AI Usage Report</t>
+  </si>
+  <si>
+    <t>ALL</t>
+  </si>
+  <si>
+    <t>Group Peer Evaluations</t>
+  </si>
+  <si>
     <t>Not started</t>
-  </si>
-  <si>
-    <t>AI Usage Report</t>
-  </si>
-  <si>
-    <t>ALL</t>
-  </si>
-  <si>
-    <t>Group Peer Evaluations</t>
   </si>
 </sst>
 </file>
@@ -671,15 +671,15 @@
         <v>15</v>
       </c>
       <c r="C10" t="s">
-        <v>22</v>
+        <v>7</v>
       </c>
     </row>
     <row r="11" spans="1:5">
       <c r="A11" t="s">
+        <v>22</v>
+      </c>
+      <c r="B11" t="s">
         <v>23</v>
-      </c>
-      <c r="B11" t="s">
-        <v>24</v>
       </c>
       <c r="C11" t="s">
         <v>18</v>
@@ -687,13 +687,13 @@
     </row>
     <row r="12" spans="1:5">
       <c r="A12" t="s">
+        <v>24</v>
+      </c>
+      <c r="B12" t="s">
+        <v>23</v>
+      </c>
+      <c r="C12" t="s">
         <v>25</v>
-      </c>
-      <c r="B12" t="s">
-        <v>24</v>
-      </c>
-      <c r="C12" t="s">
-        <v>22</v>
       </c>
     </row>
   </sheetData>

--- a/CSCI330 Group Project Task Tracker.xlsx
+++ b/CSCI330 Group Project Task Tracker.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30520"/>
-  <workbookPr/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
+  <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://marietta0-my.sharepoint.com/personal/mca003_marietta_edu/Documents/Junior Year/F26/CSCI330/Group Project/Web-Design-and-Programming-GroupWork/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="43" documentId="8_{2C5AEFBD-5EE4-4783-87B6-0456A0AA740F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F4F3F39E-77E7-4E3D-9235-29C9185504D7}"/>
+  <xr:revisionPtr revIDLastSave="58" documentId="8_{DA7DD34A-3871-4552-B4C9-0B224A20E188}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7F6A5FAB-AFE7-47E1-ACB1-A9D1F95A9BF3}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{35008FAE-AE0E-4657-A8AE-48045A98CB38}"/>
+    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{35008FAE-AE0E-4657-A8AE-48045A98CB38}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="41">
   <si>
     <t>Task</t>
   </si>
@@ -50,80 +50,125 @@
     <t>Progress</t>
   </si>
   <si>
+    <t>Home page</t>
+  </si>
+  <si>
+    <t>Maisee</t>
+  </si>
+  <si>
+    <t>In progress</t>
+  </si>
+  <si>
+    <t>Enroll student</t>
+  </si>
+  <si>
+    <t>Beatrice</t>
+  </si>
+  <si>
+    <t>Add instructor</t>
+  </si>
+  <si>
+    <t>Add course</t>
+  </si>
+  <si>
+    <t>Not started</t>
+  </si>
+  <si>
+    <t>Register course</t>
+  </si>
+  <si>
+    <t>Drew</t>
+  </si>
+  <si>
+    <t>Drop course</t>
+  </si>
+  <si>
+    <t>CSS</t>
+  </si>
+  <si>
+    <t>Manuals</t>
+  </si>
+  <si>
+    <t>README file</t>
+  </si>
+  <si>
+    <t>AI Usage Report</t>
+  </si>
+  <si>
+    <t>ALL</t>
+  </si>
+  <si>
+    <t>Group Peer Evaluations</t>
+  </si>
+  <si>
+    <t>Completed</t>
+  </si>
+  <si>
     <t>Last Updated</t>
   </si>
   <si>
     <t>Notes</t>
   </si>
   <si>
-    <t>Home page</t>
-  </si>
-  <si>
-    <t>Maisee</t>
-  </si>
-  <si>
-    <t>Completed</t>
-  </si>
-  <si>
     <t>HTML done, needs CSS applied</t>
   </si>
   <si>
-    <t>Enroll student</t>
-  </si>
-  <si>
-    <t>Beatrice</t>
-  </si>
-  <si>
-    <t>Need to apply CSS</t>
-  </si>
-  <si>
-    <t>Add instructor</t>
-  </si>
-  <si>
-    <t>Add course</t>
-  </si>
-  <si>
-    <t>Register course</t>
-  </si>
-  <si>
-    <t>Drew</t>
-  </si>
-  <si>
-    <t>Drop course</t>
-  </si>
-  <si>
-    <t>CSS</t>
-  </si>
-  <si>
-    <t>In progress</t>
-  </si>
-  <si>
-    <t>Manuals</t>
-  </si>
-  <si>
-    <t>Done with user manual(needs css),started programmer manual</t>
-  </si>
-  <si>
-    <t>README file</t>
-  </si>
-  <si>
-    <t>AI Usage Report</t>
-  </si>
-  <si>
-    <t>ALL</t>
-  </si>
-  <si>
-    <t>Group Peer Evaluations</t>
-  </si>
-  <si>
-    <t>Not started</t>
+    <t>need to apply css</t>
+  </si>
+  <si>
+    <t>Maisee, Beatrice</t>
+  </si>
+  <si>
+    <t>MODULE TWO</t>
+  </si>
+  <si>
+    <t>Enroll Student form display</t>
+  </si>
+  <si>
+    <t>Add Instructor form display</t>
+  </si>
+  <si>
+    <t>Add Course form display</t>
+  </si>
+  <si>
+    <t>Register Course form display</t>
+  </si>
+  <si>
+    <t>Drop Course form display</t>
+  </si>
+  <si>
+    <t>Updating manuals</t>
+  </si>
+  <si>
+    <t>Update select list display for Add Course</t>
+  </si>
+  <si>
+    <t>Enroll Student validation (4 rules)</t>
+  </si>
+  <si>
+    <t>Add Instructor validation (4 rules)</t>
+  </si>
+  <si>
+    <t>Add Course validation (9 rules)</t>
+  </si>
+  <si>
+    <t>Register Course validation (6 rules)</t>
+  </si>
+  <si>
+    <t>Drop Course validation (6 rules)</t>
+  </si>
+  <si>
+    <t>Beatrice &amp; Maisee</t>
+  </si>
+  <si>
+    <t>Any updates/fixes from Module 1 grade</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -139,6 +184,14 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -148,7 +201,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -156,16 +209,37 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -500,17 +574,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4840B388-0DE6-4C53-AF10-25A76A976816}">
-  <dimension ref="A1:E12"/>
-  <sheetFormatPr defaultRowHeight="15" customHeight="1"/>
+  <dimension ref="A1:E29"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="19.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="34.21875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="21" customWidth="1"/>
-    <col min="3" max="3" width="17.7109375" customWidth="1"/>
-    <col min="4" max="4" width="13.28515625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="53.85546875" customWidth="1"/>
+    <col min="3" max="3" width="17.6640625" customWidth="1"/>
+    <col min="4" max="4" width="13.21875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="25.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="15.75">
+    <row r="1" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -521,182 +595,361 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="B2" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="2" spans="1:5">
-      <c r="A2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B2" t="s">
-        <v>6</v>
-      </c>
       <c r="C2" t="s">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="D2" s="2">
         <f>DATE(2026,9,17)</f>
         <v>46282</v>
       </c>
       <c r="E2" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D3" s="2">
+        <v>46284</v>
+      </c>
+      <c r="E3" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="3" spans="1:5">
-      <c r="A3" t="s">
+      <c r="B4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C4" t="s">
+        <v>20</v>
+      </c>
+      <c r="D4" s="2">
+        <v>46285</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
         <v>9</v>
       </c>
-      <c r="B3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C3" t="s">
-        <v>7</v>
-      </c>
-      <c r="D3" s="2">
-        <v>46283</v>
-      </c>
-      <c r="E3" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5">
-      <c r="A4" t="s">
-        <v>12</v>
-      </c>
-      <c r="B4" t="s">
-        <v>10</v>
-      </c>
-      <c r="C4" t="s">
-        <v>7</v>
-      </c>
-      <c r="D4" s="2">
-        <v>46283</v>
-      </c>
-      <c r="E4" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5">
-      <c r="A5" t="s">
-        <v>13</v>
-      </c>
       <c r="B5" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C5" t="s">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="D5" s="2">
         <f>DATE(2026,9,17)</f>
         <v>46282</v>
       </c>
       <c r="E5" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
+        <v>11</v>
+      </c>
+      <c r="B6" t="s">
+        <v>12</v>
+      </c>
+      <c r="C6" t="s">
+        <v>20</v>
+      </c>
+      <c r="D6" s="2">
+        <v>46285</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>13</v>
+      </c>
+      <c r="B7" t="s">
+        <v>12</v>
+      </c>
+      <c r="C7" t="s">
+        <v>20</v>
+      </c>
+      <c r="D7" s="2">
+        <v>46285</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
         <v>14</v>
       </c>
-      <c r="B6" t="s">
-        <v>15</v>
-      </c>
-      <c r="C6" t="s">
-        <v>7</v>
-      </c>
-      <c r="D6" s="2">
-        <v>46284</v>
-      </c>
-      <c r="E6" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5">
-      <c r="A7" t="s">
-        <v>16</v>
-      </c>
-      <c r="B7" t="s">
-        <v>15</v>
-      </c>
-      <c r="C7" t="s">
-        <v>7</v>
-      </c>
-      <c r="D7" s="2">
-        <v>46284</v>
-      </c>
-      <c r="E7" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5">
-      <c r="A8" t="s">
-        <v>17</v>
-      </c>
       <c r="B8" t="s">
-        <v>6</v>
+        <v>25</v>
       </c>
       <c r="C8" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D8" s="2">
         <f>DATE(2026,9,17)</f>
         <v>46282</v>
       </c>
     </row>
-    <row r="9" spans="1:5">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
+        <v>15</v>
+      </c>
+      <c r="B9" t="s">
+        <v>7</v>
+      </c>
+      <c r="C9" t="s">
+        <v>20</v>
+      </c>
+      <c r="D9" s="2">
+        <v>46284</v>
+      </c>
+      <c r="E9" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>16</v>
+      </c>
+      <c r="B10" t="s">
+        <v>12</v>
+      </c>
+      <c r="C10" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>17</v>
+      </c>
+      <c r="B11" t="s">
+        <v>18</v>
+      </c>
+      <c r="C11" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
         <v>19</v>
       </c>
-      <c r="B9" t="s">
-        <v>10</v>
-      </c>
-      <c r="C9" t="s">
+      <c r="B12" t="s">
         <v>18</v>
       </c>
-      <c r="D9" s="2">
-        <v>46283</v>
-      </c>
-      <c r="E9" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5">
-      <c r="A10" t="s">
-        <v>21</v>
-      </c>
-      <c r="B10" t="s">
-        <v>15</v>
-      </c>
-      <c r="C10" t="s">
+      <c r="C12" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A13" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="B13" s="3"/>
+      <c r="C13" s="3"/>
+      <c r="D13" s="3"/>
+      <c r="E13" s="3"/>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>34</v>
+      </c>
+      <c r="B14" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="11" spans="1:5">
-      <c r="A11" t="s">
-        <v>22</v>
-      </c>
-      <c r="B11" t="s">
-        <v>23</v>
-      </c>
-      <c r="C11" t="s">
+      <c r="C14" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>35</v>
+      </c>
+      <c r="B15" t="s">
+        <v>7</v>
+      </c>
+      <c r="C15" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>36</v>
+      </c>
+      <c r="B16" t="s">
+        <v>4</v>
+      </c>
+      <c r="C16" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>37</v>
+      </c>
+      <c r="B17" t="s">
+        <v>12</v>
+      </c>
+      <c r="C17" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
+        <v>38</v>
+      </c>
+      <c r="B18" t="s">
+        <v>12</v>
+      </c>
+      <c r="C18" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>27</v>
+      </c>
+      <c r="B19" t="s">
+        <v>7</v>
+      </c>
+      <c r="C19" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>28</v>
+      </c>
+      <c r="B20" t="s">
+        <v>7</v>
+      </c>
+      <c r="C20" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
+        <v>29</v>
+      </c>
+      <c r="B21" t="s">
+        <v>4</v>
+      </c>
+      <c r="C21" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
+        <v>30</v>
+      </c>
+      <c r="B22" t="s">
+        <v>12</v>
+      </c>
+      <c r="C22" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
+        <v>31</v>
+      </c>
+      <c r="B23" t="s">
+        <v>12</v>
+      </c>
+      <c r="C23" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
+        <v>33</v>
+      </c>
+      <c r="B24" t="s">
+        <v>4</v>
+      </c>
+      <c r="C24" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
+        <v>32</v>
+      </c>
+      <c r="B25" t="s">
+        <v>39</v>
+      </c>
+      <c r="C25" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
+        <v>16</v>
+      </c>
+      <c r="B26" t="s">
+        <v>4</v>
+      </c>
+      <c r="C26" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A27" t="s">
+        <v>17</v>
+      </c>
+      <c r="B27" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="12" spans="1:5">
-      <c r="A12" t="s">
-        <v>24</v>
-      </c>
-      <c r="B12" t="s">
-        <v>23</v>
-      </c>
-      <c r="C12" t="s">
-        <v>25</v>
+      <c r="C27" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A28" t="s">
+        <v>19</v>
+      </c>
+      <c r="B28" t="s">
+        <v>18</v>
+      </c>
+      <c r="C28" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A29" t="s">
+        <v>40</v>
+      </c>
+      <c r="B29" t="s">
+        <v>18</v>
+      </c>
+      <c r="C29" t="s">
+        <v>5</v>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A13:E13"/>
+  </mergeCells>
   <dataValidations count="1">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C2:C12" xr:uid="{1AE900CF-695F-49FE-919B-A3667E9EEDD6}">
       <formula1>"Not started, In progress, Completed, Stuck/need help"</formula1>

--- a/CSCI330 Group Project Task Tracker.xlsx
+++ b/CSCI330 Group Project Task Tracker.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://marietta0-my.sharepoint.com/personal/mca003_marietta_edu/Documents/Junior Year/F26/CSCI330/Group Project/Web-Design-and-Programming-GroupWork/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="58" documentId="8_{DA7DD34A-3871-4552-B4C9-0B224A20E188}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7F6A5FAB-AFE7-47E1-ACB1-A9D1F95A9BF3}"/>
+  <xr:revisionPtr revIDLastSave="62" documentId="8_{DA7DD34A-3871-4552-B4C9-0B224A20E188}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{11F97A06-0197-42D1-8C01-F10BFDF9B92B}"/>
   <bookViews>
-    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{35008FAE-AE0E-4657-A8AE-48045A98CB38}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{35008FAE-AE0E-4657-A8AE-48045A98CB38}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -193,12 +193,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="2">
@@ -228,18 +234,19 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -762,13 +769,13 @@
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A13" s="4" t="s">
+      <c r="A13" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="B13" s="3"/>
-      <c r="C13" s="3"/>
-      <c r="D13" s="3"/>
-      <c r="E13" s="3"/>
+      <c r="B13" s="4"/>
+      <c r="C13" s="4"/>
+      <c r="D13" s="4"/>
+      <c r="E13" s="4"/>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
@@ -793,13 +800,13 @@
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A16" t="s">
+      <c r="A16" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="B16" t="s">
+      <c r="B16" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="C16" t="s">
+      <c r="C16" s="5" t="s">
         <v>10</v>
       </c>
     </row>
@@ -848,13 +855,13 @@
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A21" t="s">
+      <c r="A21" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="B21" t="s">
+      <c r="B21" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="C21" t="s">
+      <c r="C21" s="5" t="s">
         <v>10</v>
       </c>
     </row>
@@ -881,13 +888,13 @@
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A24" t="s">
+      <c r="A24" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="B24" t="s">
+      <c r="B24" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="C24" t="s">
+      <c r="C24" s="5" t="s">
         <v>10</v>
       </c>
     </row>
@@ -903,13 +910,13 @@
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A26" t="s">
+      <c r="A26" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="B26" t="s">
+      <c r="B26" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="C26" t="s">
+      <c r="C26" s="5" t="s">
         <v>10</v>
       </c>
     </row>

--- a/CSCI330 Group Project Task Tracker.xlsx
+++ b/CSCI330 Group Project Task Tracker.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://marietta0-my.sharepoint.com/personal/mca003_marietta_edu/Documents/Junior Year/F26/CSCI330/Group Project/Web-Design-and-Programming-GroupWork/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="62" documentId="8_{DA7DD34A-3871-4552-B4C9-0B224A20E188}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{11F97A06-0197-42D1-8C01-F10BFDF9B92B}"/>
+  <xr:revisionPtr revIDLastSave="64" documentId="8_{DA7DD34A-3871-4552-B4C9-0B224A20E188}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{10CDE41F-018B-4ECA-9E19-1BF481F85B6F}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{35008FAE-AE0E-4657-A8AE-48045A98CB38}"/>
   </bookViews>
@@ -240,13 +240,13 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -769,13 +769,13 @@
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A13" s="3" t="s">
+      <c r="A13" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="B13" s="4"/>
-      <c r="C13" s="4"/>
-      <c r="D13" s="4"/>
-      <c r="E13" s="4"/>
+      <c r="B13" s="5"/>
+      <c r="C13" s="5"/>
+      <c r="D13" s="5"/>
+      <c r="E13" s="5"/>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
@@ -800,14 +800,17 @@
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A16" s="5" t="s">
+      <c r="A16" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="B16" s="5" t="s">
+      <c r="B16" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="C16" s="5" t="s">
-        <v>10</v>
+      <c r="C16" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D16" s="2">
+        <v>46315</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.3">
@@ -855,13 +858,13 @@
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A21" s="5" t="s">
+      <c r="A21" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="B21" s="5" t="s">
+      <c r="B21" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="C21" s="5" t="s">
+      <c r="C21" s="3" t="s">
         <v>10</v>
       </c>
     </row>
@@ -888,13 +891,13 @@
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A24" s="5" t="s">
+      <c r="A24" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="B24" s="5" t="s">
+      <c r="B24" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="C24" s="5" t="s">
+      <c r="C24" s="3" t="s">
         <v>10</v>
       </c>
     </row>
@@ -910,13 +913,13 @@
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A26" s="5" t="s">
+      <c r="A26" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="B26" s="5" t="s">
+      <c r="B26" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="C26" s="5" t="s">
+      <c r="C26" s="3" t="s">
         <v>10</v>
       </c>
     </row>

--- a/CSCI330 Group Project Task Tracker.xlsx
+++ b/CSCI330 Group Project Task Tracker.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://marietta0-my.sharepoint.com/personal/mca003_marietta_edu/Documents/Junior Year/F26/CSCI330/Group Project/Web-Design-and-Programming-GroupWork/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="64" documentId="8_{DA7DD34A-3871-4552-B4C9-0B224A20E188}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{10CDE41F-018B-4ECA-9E19-1BF481F85B6F}"/>
+  <xr:revisionPtr revIDLastSave="68" documentId="8_{DA7DD34A-3871-4552-B4C9-0B224A20E188}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D6276C51-32F2-4E3E-B127-9AE165704197}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{35008FAE-AE0E-4657-A8AE-48045A98CB38}"/>
+    <workbookView xWindow="1152" yWindow="1152" windowWidth="17280" windowHeight="8880" xr2:uid="{35008FAE-AE0E-4657-A8AE-48045A98CB38}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="42">
   <si>
     <t>Task</t>
   </si>
@@ -162,6 +162,9 @@
   </si>
   <si>
     <t>Any updates/fixes from Module 1 grade</t>
+  </si>
+  <si>
+    <t>Need to ask Williamson about display</t>
   </si>
 </sst>
 </file>
@@ -588,7 +591,7 @@
     <col min="2" max="2" width="21" customWidth="1"/>
     <col min="3" max="3" width="17.6640625" customWidth="1"/>
     <col min="4" max="4" width="13.21875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="25.88671875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="30.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
@@ -813,7 +816,7 @@
         <v>46315</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>37</v>
       </c>
@@ -824,7 +827,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>38</v>
       </c>
@@ -835,7 +838,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>27</v>
       </c>
@@ -846,7 +849,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>28</v>
       </c>
@@ -857,7 +860,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A21" s="3" t="s">
         <v>29</v>
       </c>
@@ -865,10 +868,16 @@
         <v>4</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
+        <v>20</v>
+      </c>
+      <c r="D21" s="2">
+        <v>46315</v>
+      </c>
+      <c r="E21" s="3" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>30</v>
       </c>
@@ -879,7 +888,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>31</v>
       </c>
@@ -890,7 +899,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A24" s="3" t="s">
         <v>33</v>
       </c>
@@ -901,7 +910,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>32</v>
       </c>
@@ -912,7 +921,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A26" s="3" t="s">
         <v>16</v>
       </c>
@@ -923,7 +932,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>17</v>
       </c>
@@ -934,7 +943,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>19</v>
       </c>
@@ -945,7 +954,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>40</v>
       </c>

--- a/CSCI330 Group Project Task Tracker.xlsx
+++ b/CSCI330 Group Project Task Tracker.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://marietta0-my.sharepoint.com/personal/mca003_marietta_edu/Documents/Junior Year/F26/CSCI330/Group Project/Web-Design-and-Programming-GroupWork/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="68" documentId="8_{DA7DD34A-3871-4552-B4C9-0B224A20E188}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D6276C51-32F2-4E3E-B127-9AE165704197}"/>
+  <xr:revisionPtr revIDLastSave="82" documentId="8_{DA7DD34A-3871-4552-B4C9-0B224A20E188}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A3620E8E-5C05-4B15-ADDE-3618234CE928}"/>
   <bookViews>
-    <workbookView xWindow="1152" yWindow="1152" windowWidth="17280" windowHeight="8880" xr2:uid="{35008FAE-AE0E-4657-A8AE-48045A98CB38}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{35008FAE-AE0E-4657-A8AE-48045A98CB38}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="41">
   <si>
     <t>Task</t>
   </si>
@@ -162,9 +162,6 @@
   </si>
   <si>
     <t>Any updates/fixes from Module 1 grade</t>
-  </si>
-  <si>
-    <t>Need to ask Williamson about display</t>
   </si>
 </sst>
 </file>
@@ -196,7 +193,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -206,6 +203,18 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="5" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -237,7 +246,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -250,6 +259,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -781,24 +793,24 @@
       <c r="E13" s="5"/>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A14" t="s">
+      <c r="A14" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="B14" t="s">
+      <c r="B14" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="C14" t="s">
+      <c r="C14" s="6" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A15" t="s">
+      <c r="A15" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="B15" t="s">
+      <c r="B15" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="C15" t="s">
+      <c r="C15" s="6" t="s">
         <v>10</v>
       </c>
     </row>
@@ -817,46 +829,46 @@
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A17" t="s">
+      <c r="A17" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="B17" t="s">
+      <c r="B17" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="C17" t="s">
+      <c r="C17" s="7" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A18" t="s">
+      <c r="A18" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="B18" t="s">
+      <c r="B18" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="C18" t="s">
+      <c r="C18" s="7" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A19" t="s">
+      <c r="A19" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="B19" t="s">
+      <c r="B19" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="C19" t="s">
+      <c r="C19" s="6" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A20" t="s">
+      <c r="A20" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="B20" t="s">
+      <c r="B20" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="C20" t="s">
+      <c r="C20" s="6" t="s">
         <v>10</v>
       </c>
     </row>
@@ -873,29 +885,27 @@
       <c r="D21" s="2">
         <v>46315</v>
       </c>
-      <c r="E21" s="3" t="s">
-        <v>41</v>
-      </c>
+      <c r="E21" s="8"/>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A22" t="s">
+      <c r="A22" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="B22" t="s">
+      <c r="B22" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="C22" t="s">
+      <c r="C22" s="7" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A23" t="s">
+      <c r="A23" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="B23" t="s">
+      <c r="B23" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="C23" t="s">
+      <c r="C23" s="7" t="s">
         <v>10</v>
       </c>
     </row>
@@ -911,13 +921,13 @@
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A25" t="s">
+      <c r="A25" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="B25" t="s">
+      <c r="B25" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="C25" t="s">
+      <c r="C25" s="6" t="s">
         <v>10</v>
       </c>
     </row>

--- a/CSCI330 Group Project Task Tracker.xlsx
+++ b/CSCI330 Group Project Task Tracker.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://marietta0-my.sharepoint.com/personal/mca003_marietta_edu/Documents/Junior Year/F26/CSCI330/Group Project/Web-Design-and-Programming-GroupWork/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="82" documentId="8_{DA7DD34A-3871-4552-B4C9-0B224A20E188}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A3620E8E-5C05-4B15-ADDE-3618234CE928}"/>
+  <xr:revisionPtr revIDLastSave="131" documentId="8_{DA7DD34A-3871-4552-B4C9-0B224A20E188}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{641B09ED-8D79-4170-8471-263790C811E3}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{35008FAE-AE0E-4657-A8AE-48045A98CB38}"/>
   </bookViews>
@@ -168,7 +168,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -184,16 +184,8 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="5">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -208,13 +200,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.59999389629810485"/>
+        <fgColor theme="8" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.59999389629810485"/>
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF0000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -246,22 +256,23 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -784,49 +795,54 @@
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A13" s="4" t="s">
+      <c r="A13" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="B13" s="5"/>
-      <c r="C13" s="5"/>
-      <c r="D13" s="5"/>
-      <c r="E13" s="5"/>
+      <c r="B13" s="3"/>
+      <c r="C13" s="3"/>
+      <c r="D13" s="3"/>
+      <c r="E13" s="3"/>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A14" s="6" t="s">
+      <c r="A14" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="B14" s="6" t="s">
+      <c r="B14" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="C14" s="6" t="s">
+      <c r="C14" s="9" t="s">
         <v>10</v>
       </c>
+      <c r="D14" s="4"/>
+      <c r="E14" s="4"/>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A15" s="6" t="s">
+      <c r="A15" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="B15" s="6" t="s">
+      <c r="B15" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="C15" s="6" t="s">
+      <c r="C15" s="9" t="s">
         <v>10</v>
       </c>
+      <c r="D15" s="4"/>
+      <c r="E15" s="4"/>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A16" s="3" t="s">
+      <c r="A16" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="B16" s="3" t="s">
+      <c r="B16" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="C16" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="D16" s="2">
+      <c r="C16" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="D16" s="6">
         <v>46315</v>
       </c>
+      <c r="E16" s="4"/>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A17" s="7" t="s">
@@ -835,9 +851,11 @@
       <c r="B17" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="C17" s="7" t="s">
+      <c r="C17" s="9" t="s">
         <v>10</v>
       </c>
+      <c r="D17" s="4"/>
+      <c r="E17" s="4"/>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A18" s="7" t="s">
@@ -846,46 +864,52 @@
       <c r="B18" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="C18" s="7" t="s">
+      <c r="C18" s="9" t="s">
         <v>10</v>
       </c>
+      <c r="D18" s="4"/>
+      <c r="E18" s="4"/>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A19" s="6" t="s">
+      <c r="A19" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="B19" s="6" t="s">
+      <c r="B19" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="C19" s="6" t="s">
+      <c r="C19" s="9" t="s">
         <v>10</v>
       </c>
+      <c r="D19" s="4"/>
+      <c r="E19" s="4"/>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A20" s="6" t="s">
+      <c r="A20" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="B20" s="6" t="s">
+      <c r="B20" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="C20" s="6" t="s">
+      <c r="C20" s="9" t="s">
         <v>10</v>
       </c>
+      <c r="D20" s="4"/>
+      <c r="E20" s="4"/>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A21" s="3" t="s">
+      <c r="A21" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="B21" s="3" t="s">
+      <c r="B21" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="C21" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="D21" s="2">
+      <c r="C21" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="D21" s="6">
         <v>46315</v>
       </c>
-      <c r="E21" s="8"/>
+      <c r="E21" s="4"/>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A22" s="7" t="s">
@@ -894,9 +918,11 @@
       <c r="B22" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="C22" s="7" t="s">
+      <c r="C22" s="9" t="s">
         <v>10</v>
       </c>
+      <c r="D22" s="4"/>
+      <c r="E22" s="4"/>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A23" s="7" t="s">
@@ -905,82 +931,98 @@
       <c r="B23" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="C23" s="7" t="s">
+      <c r="C23" s="9" t="s">
         <v>10</v>
       </c>
+      <c r="D23" s="4"/>
+      <c r="E23" s="4"/>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A24" s="3" t="s">
+      <c r="A24" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="B24" s="3" t="s">
+      <c r="B24" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="C24" s="3" t="s">
+      <c r="C24" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="D24" s="6">
+        <v>46317</v>
+      </c>
+      <c r="E24" s="4"/>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A25" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="B25" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="C25" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="D25" s="4"/>
+      <c r="E25" s="4"/>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A26" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="B26" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="C26" s="9" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A25" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="B25" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="C25" s="6" t="s">
+      <c r="D26" s="4"/>
+      <c r="E26" s="4"/>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A27" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="B27" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C27" s="9" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A26" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="B26" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="C26" s="3" t="s">
+      <c r="D27" s="4"/>
+      <c r="E27" s="4"/>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A28" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B28" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C28" s="9" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A27" t="s">
-        <v>17</v>
-      </c>
-      <c r="B27" t="s">
+      <c r="D28" s="4"/>
+      <c r="E28" s="4"/>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A29" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="B29" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="C27" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A28" t="s">
-        <v>19</v>
-      </c>
-      <c r="B28" t="s">
-        <v>18</v>
-      </c>
-      <c r="C28" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A29" t="s">
-        <v>40</v>
-      </c>
-      <c r="B29" t="s">
-        <v>18</v>
-      </c>
-      <c r="C29" t="s">
+      <c r="C29" s="8" t="s">
         <v>5</v>
       </c>
+      <c r="D29" s="4"/>
+      <c r="E29" s="4"/>
     </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A13:E13"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C2:C12" xr:uid="{1AE900CF-695F-49FE-919B-A3667E9EEDD6}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C2:C12 C15:C29 C14" xr:uid="{1AE900CF-695F-49FE-919B-A3667E9EEDD6}">
       <formula1>"Not started, In progress, Completed, Stuck/need help"</formula1>
     </dataValidation>
   </dataValidations>

--- a/CSCI330 Group Project Task Tracker.xlsx
+++ b/CSCI330 Group Project Task Tracker.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30527"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://marietta0-my.sharepoint.com/personal/mca003_marietta_edu/Documents/Junior Year/F26/CSCI330/Group Project/Web-Design-and-Programming-GroupWork/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="131" documentId="8_{DA7DD34A-3871-4552-B4C9-0B224A20E188}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{641B09ED-8D79-4170-8471-263790C811E3}"/>
+  <xr:revisionPtr revIDLastSave="133" documentId="8_{DA7DD34A-3871-4552-B4C9-0B224A20E188}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A7EC3BA0-BE38-4A4E-912A-7B6CD69751F7}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{35008FAE-AE0E-4657-A8AE-48045A98CB38}"/>
   </bookViews>
@@ -262,9 +262,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
@@ -273,6 +270,9 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -795,227 +795,227 @@
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A13" s="3" t="s">
+      <c r="A13" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="B13" s="3"/>
-      <c r="C13" s="3"/>
-      <c r="D13" s="3"/>
-      <c r="E13" s="3"/>
+      <c r="B13" s="11"/>
+      <c r="C13" s="11"/>
+      <c r="D13" s="11"/>
+      <c r="E13" s="11"/>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A14" s="10" t="s">
+      <c r="A14" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="B14" s="10" t="s">
+      <c r="B14" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="C14" s="9" t="s">
+      <c r="C14" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="4"/>
-      <c r="E14" s="4"/>
+      <c r="D14" s="3"/>
+      <c r="E14" s="3"/>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A15" s="10" t="s">
+      <c r="A15" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="B15" s="10" t="s">
+      <c r="B15" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="C15" s="9" t="s">
+      <c r="C15" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="D15" s="4"/>
-      <c r="E15" s="4"/>
+      <c r="D15" s="3"/>
+      <c r="E15" s="3"/>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A16" s="5" t="s">
+      <c r="A16" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="B16" s="5" t="s">
+      <c r="B16" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="C16" s="11" t="s">
-        <v>20</v>
-      </c>
-      <c r="D16" s="6">
+      <c r="C16" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="D16" s="5">
         <v>46315</v>
       </c>
-      <c r="E16" s="4"/>
+      <c r="E16" s="3"/>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A17" s="7" t="s">
+      <c r="A17" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="B17" s="7" t="s">
+      <c r="B17" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="C17" s="9" t="s">
+      <c r="C17" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="D17" s="4"/>
-      <c r="E17" s="4"/>
+      <c r="D17" s="3"/>
+      <c r="E17" s="3"/>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A18" s="7" t="s">
+      <c r="A18" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B18" s="7" t="s">
+      <c r="B18" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="C18" s="9" t="s">
+      <c r="C18" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="D18" s="4"/>
-      <c r="E18" s="4"/>
+      <c r="D18" s="3"/>
+      <c r="E18" s="3"/>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A19" s="10" t="s">
+      <c r="A19" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="B19" s="10" t="s">
+      <c r="B19" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="C19" s="9" t="s">
+      <c r="C19" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="D19" s="4"/>
-      <c r="E19" s="4"/>
+      <c r="D19" s="3"/>
+      <c r="E19" s="3"/>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A20" s="10" t="s">
+      <c r="A20" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="B20" s="10" t="s">
+      <c r="B20" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="C20" s="9" t="s">
+      <c r="C20" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="D20" s="4"/>
-      <c r="E20" s="4"/>
+      <c r="D20" s="3"/>
+      <c r="E20" s="3"/>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A21" s="5" t="s">
+      <c r="A21" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="B21" s="5" t="s">
+      <c r="B21" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="C21" s="11" t="s">
-        <v>20</v>
-      </c>
-      <c r="D21" s="6">
+      <c r="C21" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="D21" s="5">
         <v>46315</v>
       </c>
-      <c r="E21" s="4"/>
+      <c r="E21" s="3"/>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A22" s="7" t="s">
+      <c r="A22" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="B22" s="7" t="s">
+      <c r="B22" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="C22" s="9" t="s">
+      <c r="C22" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="D22" s="4"/>
-      <c r="E22" s="4"/>
+      <c r="D22" s="3"/>
+      <c r="E22" s="3"/>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A23" s="7" t="s">
+      <c r="A23" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="B23" s="7" t="s">
+      <c r="B23" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="C23" s="9" t="s">
+      <c r="C23" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="D23" s="4"/>
-      <c r="E23" s="4"/>
+      <c r="D23" s="3"/>
+      <c r="E23" s="3"/>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A24" s="5" t="s">
+      <c r="A24" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="B24" s="5" t="s">
+      <c r="B24" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="C24" s="11" t="s">
-        <v>20</v>
-      </c>
-      <c r="D24" s="6">
+      <c r="C24" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="D24" s="5">
         <v>46317</v>
       </c>
-      <c r="E24" s="4"/>
+      <c r="E24" s="3"/>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A25" s="10" t="s">
+      <c r="A25" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="B25" s="5" t="s">
+      <c r="B25" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="C25" s="8" t="s">
+      <c r="C25" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="D25" s="4"/>
-      <c r="E25" s="4"/>
+      <c r="D25" s="3"/>
+      <c r="E25" s="3"/>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A26" s="5" t="s">
+      <c r="A26" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="B26" s="5" t="s">
+      <c r="B26" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="C26" s="9" t="s">
+      <c r="C26" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="D26" s="4"/>
-      <c r="E26" s="4"/>
+      <c r="D26" s="3"/>
+      <c r="E26" s="3"/>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A27" s="4" t="s">
+      <c r="A27" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="B27" s="4" t="s">
+      <c r="B27" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="C27" s="9" t="s">
+      <c r="C27" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="D27" s="4"/>
-      <c r="E27" s="4"/>
+      <c r="D27" s="3"/>
+      <c r="E27" s="3"/>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A28" s="4" t="s">
+      <c r="A28" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="B28" s="4" t="s">
+      <c r="B28" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="C28" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="D28" s="4"/>
-      <c r="E28" s="4"/>
+      <c r="C28" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="D28" s="3"/>
+      <c r="E28" s="3"/>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A29" s="4" t="s">
+      <c r="A29" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B29" s="4" t="s">
+      <c r="B29" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="C29" s="8" t="s">
+      <c r="C29" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="D29" s="4"/>
-      <c r="E29" s="4"/>
+      <c r="D29" s="3"/>
+      <c r="E29" s="3"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/CSCI330 Group Project Task Tracker.xlsx
+++ b/CSCI330 Group Project Task Tracker.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30527"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30619"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://marietta0-my.sharepoint.com/personal/mca003_marietta_edu/Documents/Junior Year/F26/CSCI330/Group Project/Web-Design-and-Programming-GroupWork/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="133" documentId="8_{DA7DD34A-3871-4552-B4C9-0B224A20E188}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A7EC3BA0-BE38-4A4E-912A-7B6CD69751F7}"/>
+  <xr:revisionPtr revIDLastSave="150" documentId="8_{DA7DD34A-3871-4552-B4C9-0B224A20E188}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{410288C3-DFF8-43D2-ABC0-8A2A44450946}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{35008FAE-AE0E-4657-A8AE-48045A98CB38}"/>
   </bookViews>
@@ -50,112 +50,112 @@
     <t>Progress</t>
   </si>
   <si>
+    <t>Last Updated</t>
+  </si>
+  <si>
+    <t>Notes</t>
+  </si>
+  <si>
     <t>Home page</t>
   </si>
   <si>
     <t>Maisee</t>
   </si>
   <si>
+    <t>Completed</t>
+  </si>
+  <si>
+    <t>HTML done, needs CSS applied</t>
+  </si>
+  <si>
+    <t>Enroll student</t>
+  </si>
+  <si>
+    <t>Beatrice</t>
+  </si>
+  <si>
+    <t>need to apply css</t>
+  </si>
+  <si>
+    <t>Add instructor</t>
+  </si>
+  <si>
+    <t>Add course</t>
+  </si>
+  <si>
+    <t>Register course</t>
+  </si>
+  <si>
+    <t>Drew</t>
+  </si>
+  <si>
+    <t>Drop course</t>
+  </si>
+  <si>
+    <t>CSS</t>
+  </si>
+  <si>
+    <t>Maisee, Beatrice</t>
+  </si>
+  <si>
+    <t>Manuals</t>
+  </si>
+  <si>
+    <t>README file</t>
+  </si>
+  <si>
+    <t>AI Usage Report</t>
+  </si>
+  <si>
+    <t>ALL</t>
+  </si>
+  <si>
+    <t>Group Peer Evaluations</t>
+  </si>
+  <si>
+    <t>MODULE TWO</t>
+  </si>
+  <si>
+    <t>Enroll Student validation (4 rules)</t>
+  </si>
+  <si>
+    <t>Add Instructor validation (4 rules)</t>
+  </si>
+  <si>
+    <t>Add Course validation (9 rules)</t>
+  </si>
+  <si>
+    <t>Register Course validation (6 rules)</t>
+  </si>
+  <si>
     <t>In progress</t>
   </si>
   <si>
-    <t>Enroll student</t>
-  </si>
-  <si>
-    <t>Beatrice</t>
-  </si>
-  <si>
-    <t>Add instructor</t>
-  </si>
-  <si>
-    <t>Add course</t>
+    <t>Drop Course validation (6 rules)</t>
+  </si>
+  <si>
+    <t>Enroll Student form display</t>
+  </si>
+  <si>
+    <t>Add Instructor form display</t>
+  </si>
+  <si>
+    <t>Add Course form display</t>
+  </si>
+  <si>
+    <t>Register Course form display</t>
   </si>
   <si>
     <t>Not started</t>
   </si>
   <si>
-    <t>Register course</t>
-  </si>
-  <si>
-    <t>Drew</t>
-  </si>
-  <si>
-    <t>Drop course</t>
-  </si>
-  <si>
-    <t>CSS</t>
-  </si>
-  <si>
-    <t>Manuals</t>
-  </si>
-  <si>
-    <t>README file</t>
-  </si>
-  <si>
-    <t>AI Usage Report</t>
-  </si>
-  <si>
-    <t>ALL</t>
-  </si>
-  <si>
-    <t>Group Peer Evaluations</t>
-  </si>
-  <si>
-    <t>Completed</t>
-  </si>
-  <si>
-    <t>Last Updated</t>
-  </si>
-  <si>
-    <t>Notes</t>
-  </si>
-  <si>
-    <t>HTML done, needs CSS applied</t>
-  </si>
-  <si>
-    <t>need to apply css</t>
-  </si>
-  <si>
-    <t>Maisee, Beatrice</t>
-  </si>
-  <si>
-    <t>MODULE TWO</t>
-  </si>
-  <si>
-    <t>Enroll Student form display</t>
-  </si>
-  <si>
-    <t>Add Instructor form display</t>
-  </si>
-  <si>
-    <t>Add Course form display</t>
-  </si>
-  <si>
-    <t>Register Course form display</t>
-  </si>
-  <si>
     <t>Drop Course form display</t>
   </si>
   <si>
+    <t>Update select list display for Add Course</t>
+  </si>
+  <si>
     <t>Updating manuals</t>
-  </si>
-  <si>
-    <t>Update select list display for Add Course</t>
-  </si>
-  <si>
-    <t>Enroll Student validation (4 rules)</t>
-  </si>
-  <si>
-    <t>Add Instructor validation (4 rules)</t>
-  </si>
-  <si>
-    <t>Add Course validation (9 rules)</t>
-  </si>
-  <si>
-    <t>Register Course validation (6 rules)</t>
-  </si>
-  <si>
-    <t>Drop Course validation (6 rules)</t>
   </si>
   <si>
     <t>Beatrice &amp; Maisee</t>
@@ -168,7 +168,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -608,16 +608,16 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4840B388-0DE6-4C53-AF10-25A76A976816}">
   <dimension ref="A1:E29"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.45"/>
   <cols>
-    <col min="1" max="1" width="34.21875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="34.28515625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="21" customWidth="1"/>
-    <col min="3" max="3" width="17.6640625" customWidth="1"/>
-    <col min="4" max="4" width="13.21875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="30.88671875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.7109375" customWidth="1"/>
+    <col min="4" max="4" width="13.28515625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="30.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" ht="15.6">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -628,391 +628,391 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>21</v>
+        <v>3</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
       <c r="A2" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="B2" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C2" t="s">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="D2" s="2">
         <f>DATE(2026,9,17)</f>
         <v>46282</v>
       </c>
       <c r="E2" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
       <c r="A3" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="B3" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="C3" t="s">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="D3" s="2">
         <v>46284</v>
       </c>
       <c r="E3" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
       <c r="A4" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="B4" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="C4" t="s">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="D4" s="2">
         <v>46285</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:5">
       <c r="A5" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="B5" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C5" t="s">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="D5" s="2">
         <f>DATE(2026,9,17)</f>
         <v>46282</v>
       </c>
       <c r="E5" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5">
       <c r="A6" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="B6" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="C6" t="s">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="D6" s="2">
         <v>46285</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:5">
       <c r="A7" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="B7" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="C7" t="s">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="D7" s="2">
         <v>46285</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:5">
       <c r="A8" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="B8" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="C8" t="s">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="D8" s="2">
         <f>DATE(2026,9,17)</f>
         <v>46282</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:5">
       <c r="A9" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="B9" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="C9" t="s">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="D9" s="2">
         <v>46284</v>
       </c>
       <c r="E9" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5">
+      <c r="A10" t="s">
+        <v>20</v>
+      </c>
+      <c r="B10" t="s">
+        <v>15</v>
+      </c>
+      <c r="C10" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5">
+      <c r="A11" t="s">
+        <v>21</v>
+      </c>
+      <c r="B11" t="s">
+        <v>22</v>
+      </c>
+      <c r="C11" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5">
+      <c r="A12" t="s">
+        <v>23</v>
+      </c>
+      <c r="B12" t="s">
+        <v>22</v>
+      </c>
+      <c r="C12" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5">
+      <c r="A13" s="11" t="s">
         <v>24</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
-        <v>16</v>
-      </c>
-      <c r="B10" t="s">
-        <v>12</v>
-      </c>
-      <c r="C10" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A11" t="s">
-        <v>17</v>
-      </c>
-      <c r="B11" t="s">
-        <v>18</v>
-      </c>
-      <c r="C11" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A12" t="s">
-        <v>19</v>
-      </c>
-      <c r="B12" t="s">
-        <v>18</v>
-      </c>
-      <c r="C12" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A13" s="11" t="s">
-        <v>26</v>
       </c>
       <c r="B13" s="11"/>
       <c r="C13" s="11"/>
       <c r="D13" s="11"/>
       <c r="E13" s="11"/>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:5">
       <c r="A14" s="9" t="s">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>7</v>
-      </c>
-      <c r="C14" s="8" t="s">
         <v>10</v>
+      </c>
+      <c r="C14" s="10" t="s">
+        <v>7</v>
       </c>
       <c r="D14" s="3"/>
       <c r="E14" s="3"/>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:5">
       <c r="A15" s="9" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>7</v>
-      </c>
-      <c r="C15" s="8" t="s">
         <v>10</v>
+      </c>
+      <c r="C15" s="10" t="s">
+        <v>7</v>
       </c>
       <c r="D15" s="3"/>
       <c r="E15" s="3"/>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:5">
       <c r="A16" s="4" t="s">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C16" s="10" t="s">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="D16" s="5">
         <v>46315</v>
       </c>
       <c r="E16" s="3"/>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:5">
       <c r="A17" s="6" t="s">
-        <v>37</v>
+        <v>28</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="C17" s="8" t="s">
-        <v>10</v>
+        <v>15</v>
+      </c>
+      <c r="C17" s="7" t="s">
+        <v>29</v>
       </c>
       <c r="D17" s="3"/>
       <c r="E17" s="3"/>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:5">
       <c r="A18" s="6" t="s">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="C18" s="8" t="s">
-        <v>10</v>
+        <v>15</v>
+      </c>
+      <c r="C18" s="7" t="s">
+        <v>29</v>
       </c>
       <c r="D18" s="3"/>
       <c r="E18" s="3"/>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:5">
       <c r="A19" s="9" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="B19" s="9" t="s">
-        <v>7</v>
-      </c>
-      <c r="C19" s="8" t="s">
         <v>10</v>
+      </c>
+      <c r="C19" s="10" t="s">
+        <v>7</v>
       </c>
       <c r="D19" s="3"/>
       <c r="E19" s="3"/>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:5">
       <c r="A20" s="9" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="B20" s="9" t="s">
-        <v>7</v>
-      </c>
-      <c r="C20" s="8" t="s">
         <v>10</v>
+      </c>
+      <c r="C20" s="10" t="s">
+        <v>7</v>
       </c>
       <c r="D20" s="3"/>
       <c r="E20" s="3"/>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:5">
       <c r="A21" s="4" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C21" s="10" t="s">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="D21" s="5">
         <v>46315</v>
       </c>
       <c r="E21" s="3"/>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:5">
       <c r="A22" s="6" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="C22" s="8" t="s">
-        <v>10</v>
+        <v>35</v>
       </c>
       <c r="D22" s="3"/>
       <c r="E22" s="3"/>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:5">
       <c r="A23" s="6" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="C23" s="8" t="s">
-        <v>10</v>
+        <v>35</v>
       </c>
       <c r="D23" s="3"/>
       <c r="E23" s="3"/>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:5">
       <c r="A24" s="4" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C24" s="10" t="s">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="D24" s="5">
         <v>46317</v>
       </c>
       <c r="E24" s="3"/>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:5">
       <c r="A25" s="9" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="B25" s="4" t="s">
         <v>39</v>
       </c>
       <c r="C25" s="7" t="s">
-        <v>5</v>
+        <v>29</v>
       </c>
       <c r="D25" s="3"/>
       <c r="E25" s="3"/>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:5">
       <c r="A26" s="4" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C26" s="8" t="s">
-        <v>10</v>
+        <v>35</v>
       </c>
       <c r="D26" s="3"/>
       <c r="E26" s="3"/>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:5">
       <c r="A27" s="3" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="C27" s="8" t="s">
-        <v>10</v>
+        <v>35</v>
       </c>
       <c r="D27" s="3"/>
       <c r="E27" s="3"/>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:5">
       <c r="A28" s="3" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="C28" s="7" t="s">
-        <v>5</v>
+        <v>29</v>
       </c>
       <c r="D28" s="3"/>
       <c r="E28" s="3"/>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:5">
       <c r="A29" s="3" t="s">
         <v>40</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="C29" s="7" t="s">
-        <v>5</v>
+        <v>29</v>
       </c>
       <c r="D29" s="3"/>
       <c r="E29" s="3"/>
